--- a/nr-update-commune/ig/StructureDefinition-fr-core-organization-activity-field.xlsx
+++ b/nr-update-commune/ig/StructureDefinition-fr-core-organization-activity-field.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T08:33:31+00:00</t>
+    <t>2024-07-25T08:34:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-commune/ig/StructureDefinition-fr-core-organization-activity-field.xlsx
+++ b/nr-update-commune/ig/StructureDefinition-fr-core-organization-activity-field.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T08:34:13+00:00</t>
+    <t>2024-07-25T15:15:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
